--- a/test-case-exports/Reconciliation.xlsx
+++ b/test-case-exports/Reconciliation.xlsx
@@ -125,73 +125,73 @@
     <t>Reconciliation – External (Bank → System)</t>
   </si>
   <si>
-    <t>RC-01: importing a bank statement flags a transaction missing from the system</t>
+    <t>RCN-01: importing a bank statement flags a transaction missing from the system</t>
   </si>
   <si>
     <t>Skipped: pending Admin Portal / Reconciliation Ops tooling access (EMI-4537/EMI-2177)</t>
   </si>
   <si>
-    <t>RC-02: importing a bank statement flags an amount/status/date discrepancy</t>
-  </si>
-  <si>
-    <t>RC-03: bank omnibus balance vs system Control Wallet mismatch is flagged</t>
-  </si>
-  <si>
-    <t>RC-04: a missing bank transaction is auto-inserted with correct reconciliation metadata</t>
-  </si>
-  <si>
-    <t>RC-05: an auto-inserted transaction correctly impacts running_balance</t>
-  </si>
-  <si>
-    <t>RC-06: all external reconciliation actions are logged in reconciliation_runs</t>
+    <t>RCN-02: importing a bank statement flags an amount/status/date discrepancy</t>
+  </si>
+  <si>
+    <t>RCN-03: bank omnibus balance vs system Control Wallet mismatch is flagged</t>
+  </si>
+  <si>
+    <t>RCN-04: a missing bank transaction is auto-inserted with correct reconciliation metadata</t>
+  </si>
+  <si>
+    <t>RCN-05: an auto-inserted transaction correctly impacts running_balance</t>
+  </si>
+  <si>
+    <t>RCN-06: all external reconciliation actions are logged in reconciliation_runs</t>
   </si>
   <si>
     <t>Reconciliation – Internal (System Ledger → Wallet Balances)</t>
   </si>
   <si>
-    <t>RC-07: a running_balance vs transaction_log mismatch triggers a rebuild</t>
-  </si>
-  <si>
-    <t>RC-08: a wallet whose last running_balance record differs from its wallet-table balance is flagged</t>
-  </si>
-  <si>
-    <t>RC-09: sum of all wallet balances differing from the control wallet balance is flagged</t>
-  </si>
-  <si>
-    <t>RC-10: a manually triggered running-balance rebuild (Admin UI) succeeds for a date range</t>
-  </si>
-  <si>
-    <t>RC-11: the scheduled (nightly) running-balance rebuild job succeeds</t>
-  </si>
-  <si>
-    <t>RC-12: the rebuild job archives existing entries to running_balance_history before rebuilding</t>
-  </si>
-  <si>
-    <t>RC-13: the rebuild job updates the wallets table with the correct last-valid-TXN balance</t>
+    <t>RCN-07: a running_balance vs transaction_log mismatch triggers a rebuild</t>
+  </si>
+  <si>
+    <t>RCN-08: a wallet whose last running_balance record differs from its wallet-table balance is flagged</t>
+  </si>
+  <si>
+    <t>RCN-09: sum of all wallet balances differing from the control wallet balance is flagged</t>
+  </si>
+  <si>
+    <t>RCN-10: a manually triggered running-balance rebuild (Admin UI) succeeds for a date range</t>
+  </si>
+  <si>
+    <t>RCN-11: the scheduled (nightly) running-balance rebuild job succeeds</t>
+  </si>
+  <si>
+    <t>RCN-12: the rebuild job archives existing entries to running_balance_history before rebuilding</t>
+  </si>
+  <si>
+    <t>RCN-13: the rebuild job updates the wallets table with the correct last-valid-TXN balance</t>
   </si>
   <si>
     <t>Reconciliation – Dynamic Reconciliation Management System (DRMS)</t>
   </si>
   <si>
-    <t>RC-14: a custom reconciliation matching rule can be configured and applied (EMI-4541 Rules Engine)</t>
-  </si>
-  <si>
-    <t>RC-15: two systems' records can be linked for matching (EMI-4542 Pair Management)</t>
-  </si>
-  <si>
-    <t>RC-16: a new reconciliation data source can be registered and configured (EMI-4543 Systems Management)</t>
-  </si>
-  <si>
-    <t>RC-17: external system fields can be mapped to the unified schema (EMI-4549 System Types &amp; Unified Schema)</t>
-  </si>
-  <si>
-    <t>RC-18: a file/API ingestion source can be configured (EMI-4550 Ingestion Configuration &amp; Data Mapping)</t>
-  </si>
-  <si>
-    <t>RC-19: a reconciliation run can be manually triggered and a report generated (EMI-4551 Run Execution &amp; Report Generation)</t>
-  </si>
-  <si>
-    <t>RC-20: a generated reconciliation report can be exported/downloaded</t>
+    <t>RCN-14: a custom reconciliation matching rule can be configured and applied (EMI-4541 Rules Engine)</t>
+  </si>
+  <si>
+    <t>RCN-15: two systems' records can be linked for matching (EMI-4542 Pair Management)</t>
+  </si>
+  <si>
+    <t>RCN-16: a new reconciliation data source can be registered and configured (EMI-4543 Systems Management)</t>
+  </si>
+  <si>
+    <t>RCN-17: external system fields can be mapped to the unified schema (EMI-4549 System Types &amp; Unified Schema)</t>
+  </si>
+  <si>
+    <t>RCN-18: a file/API ingestion source can be configured (EMI-4550 Ingestion Configuration &amp; Data Mapping)</t>
+  </si>
+  <si>
+    <t>RCN-19: a reconciliation run can be manually triggered and a report generated (EMI-4551 Run Execution &amp; Report Generation)</t>
+  </si>
+  <si>
+    <t>RCN-20: a generated reconciliation report can be exported/downloaded</t>
   </si>
   <si>
     <t>Summary — Reconciliation</t>
@@ -200,7 +200,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-09-08T15:08:53.615Z</t>
+    <t>2026-09-09T06:44:10.188Z</t>
   </si>
   <si>
     <t>Total test cases</t>
